--- a/Additional Material/Public Finance.xlsx
+++ b/Additional Material/Public Finance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Teaching\Public Finance\PublicFinanceGitHub\Additional Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851B112C-8681-40C2-9AD5-CC2B0A4B454C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0C0E60-1D5B-47BD-B04C-DA2D8927E70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32811" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Line Item Budget" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,46 @@
     <sheet name="HRD Parameters" sheetId="5" r:id="rId3"/>
     <sheet name="HRD Budget" sheetId="6" r:id="rId4"/>
     <sheet name="SPEAville Police" sheetId="7" r:id="rId5"/>
+    <sheet name="PARK CONGESTION" sheetId="9" r:id="rId6"/>
+    <sheet name="STATE TAXE REFORM" sheetId="8" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="Planted">#REF!</definedName>
+    <definedName name="solver_adj" localSheetId="5" hidden="1">'PARK CONGESTION'!$B$8</definedName>
+    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="5" hidden="1">'PARK CONGESTION'!$B$8</definedName>
+    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="5" hidden="1">'PARK CONGESTION'!$B$13</definedName>
+    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="5" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="5" hidden="1">0.01</definedName>
+    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
+    <definedName name="STC13_2">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="195">
   <si>
     <t>Operating Expenditures Total</t>
   </si>
@@ -504,20 +543,178 @@
   <si>
     <t>Budgeted Positions O'Neill PD</t>
   </si>
+  <si>
+    <t>Case Study: State Taxes</t>
+  </si>
+  <si>
+    <t>Household</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Alpha Gasoline</t>
+  </si>
+  <si>
+    <t>Alpha Food</t>
+  </si>
+  <si>
+    <t>Alpha Other Goods</t>
+  </si>
+  <si>
+    <t>Income Before State Income Tax</t>
+  </si>
+  <si>
+    <t>State Income Tax Rate (%)</t>
+  </si>
+  <si>
+    <t>Sales Tax Rate (%)</t>
+  </si>
+  <si>
+    <t>Gasoline Tax Rate ($)</t>
+  </si>
+  <si>
+    <t>Wholesale Price: Gasoline ($)</t>
+  </si>
+  <si>
+    <t>Wholesale Price: Food ($)</t>
+  </si>
+  <si>
+    <t>Wholesale Price: Other Goods ($)</t>
+  </si>
+  <si>
+    <t>State Income Tax Revenue ($)</t>
+  </si>
+  <si>
+    <t>Income After State Income Tax ($)</t>
+  </si>
+  <si>
+    <t>Gasoline Retail Price ($)</t>
+  </si>
+  <si>
+    <t>Gasoline Quantity Demanded</t>
+  </si>
+  <si>
+    <t>Gasoline Total Expenditure ($)</t>
+  </si>
+  <si>
+    <t>Gasoline Tax Expenditure ($)</t>
+  </si>
+  <si>
+    <t>Gasoline Effective Tax Rate (%)</t>
+  </si>
+  <si>
+    <t>Food Retail Price ($)</t>
+  </si>
+  <si>
+    <t>Food Quantity Demanded</t>
+  </si>
+  <si>
+    <t>Food Total Expenditure ($)</t>
+  </si>
+  <si>
+    <t>Food Tax Expenditure ($)</t>
+  </si>
+  <si>
+    <t>Food Effective Tax Rate (%)</t>
+  </si>
+  <si>
+    <t>Other Goods Retail Price ($)</t>
+  </si>
+  <si>
+    <t>Other Goods Quantity Demanded</t>
+  </si>
+  <si>
+    <t>Other Goods Total Expenditure ($)</t>
+  </si>
+  <si>
+    <t>Other Goods Tax Expenditure ($)</t>
+  </si>
+  <si>
+    <t>Other Goods Effective Tax Rate (%)</t>
+  </si>
+  <si>
+    <t>Total Tax Expenditures ($)</t>
+  </si>
+  <si>
+    <t>Effective Tax Rate All Taxes (%)</t>
+  </si>
+  <si>
+    <t>Total Surplus</t>
+  </si>
+  <si>
+    <t>Benefit per Person</t>
+  </si>
+  <si>
+    <t>Tax per Person</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Park Size (G)</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>phi</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -651,8 +848,28 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -662,6 +879,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -858,13 +1081,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -935,299 +1159,375 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="14" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="14" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="14" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="14" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{940B43CE-EE2C-43D4-A4B2-C69566EE2322}"/>
@@ -1244,6 +1544,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="STATE TAXES"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1787,14 +2104,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
     </row>
     <row r="2" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14"/>
@@ -1910,12 +2227,12 @@
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
@@ -2011,12 +2328,12 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
     </row>
     <row r="20" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
@@ -2113,14 +2430,14 @@
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="107"/>
     </row>
     <row r="28" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="9" t="s">
@@ -2551,236 +2868,236 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="20.69140625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="60.69140625" style="26" customWidth="1"/>
-    <col min="2" max="16384" width="20.69140625" style="26"/>
+    <col min="1" max="1" width="60.69140625" style="24" customWidth="1"/>
+    <col min="2" max="16384" width="20.69140625" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="44"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="2" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="37"/>
-      <c r="B2" s="46" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="43" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="29">
         <v>41000</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="29">
         <v>180000</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="29">
         <f>SUM(B4:C4)</f>
         <v>221000</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="28">
         <v>80</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="28">
         <v>185</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="28">
         <f>SUM(B5:C5)</f>
         <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="29">
         <f>B4/B5</f>
         <v>512.5</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="29">
         <f>C4/C5</f>
         <v>972.97297297297303</v>
       </c>
-      <c r="D6" s="30"/>
+      <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="28">
         <v>4</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="28">
         <v>5</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="28">
         <f>SUM(B7:C7)</f>
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="26">
         <v>225</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="26">
         <v>225</v>
       </c>
-      <c r="D8" s="28"/>
+      <c r="D8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="40">
         <v>6250</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="40">
         <v>10200</v>
       </c>
-      <c r="D9" s="41"/>
+      <c r="D9" s="39"/>
     </row>
     <row r="10" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
     </row>
     <row r="11" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="37">
         <f>B5/B7</f>
         <v>20</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="37">
         <f>C5/C7</f>
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="36">
         <v>25</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="36">
         <v>50</v>
       </c>
-      <c r="D12" s="37"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="29">
         <v>74000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="29">
         <v>74000</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31">
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29">
         <v>96000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31">
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29">
         <v>61000</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="29">
         <v>6250</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="29">
         <v>9750</v>
       </c>
-      <c r="D17" s="30"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="29">
         <v>725</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="29">
         <v>1100</v>
       </c>
-      <c r="D18" s="30"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="26">
         <v>12</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="26">
         <v>12</v>
       </c>
-      <c r="D19" s="28"/>
+      <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="27">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="25">
         <v>210000</v>
       </c>
     </row>
@@ -2804,692 +3121,692 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="20.69140625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="45.69140625" style="48" customWidth="1"/>
-    <col min="2" max="16384" width="20.69140625" style="48"/>
+    <col min="1" max="1" width="45.69140625" style="45" customWidth="1"/>
+    <col min="2" max="16384" width="20.69140625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="89"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="111"/>
     </row>
     <row r="2" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="88"/>
-      <c r="B2" s="87" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="112" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="87" t="s">
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="112" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="86"/>
-      <c r="G2" s="85"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="114"/>
     </row>
     <row r="3" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="52"/>
-      <c r="B3" s="84" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="F3" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="79" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="81"/>
-      <c r="G4" s="80"/>
+      <c r="B4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="71">
+      <c r="B5" s="68">
         <f>'HRD Parameters'!B5</f>
         <v>80</v>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="67">
         <f>'HRD Parameters'!C5</f>
         <v>185</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="62">
         <f>SUM(B5:C5)</f>
         <v>265</v>
       </c>
-      <c r="E5" s="71">
+      <c r="E5" s="68">
         <f>B5</f>
         <v>80</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="67">
         <f>C5</f>
         <v>185</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="62">
         <f>SUM(E5:F5)</f>
         <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="75">
         <f>B5/($B5+$C5)</f>
         <v>0.30188679245283018</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="74">
         <f>C5/($B5+$C5)</f>
         <v>0.69811320754716977</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="73">
         <f>D5/($B5+$C5)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="75">
         <f>E5/($E5+$F5)</f>
         <v>0.30188679245283018</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F6" s="74">
         <f>F5/($E5+$F5)</f>
         <v>0.69811320754716977</v>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="73">
         <f>G5/($E5+$F5)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="72">
         <f>B5/'HRD Parameters'!B$11</f>
         <v>4</v>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="71">
         <f>C5/'HRD Parameters'!C$11</f>
         <v>5</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="70">
         <f>SUM(B7:C7)</f>
         <v>9</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="72">
         <f>ROUNDUP(E5/'HRD Parameters'!B$12,0)</f>
         <v>4</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="71">
         <f>ROUNDUP(F5/'HRD Parameters'!C$12,0)</f>
         <v>4</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="70">
         <f>SUM(E7:F7)</f>
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="69">
+      <c r="B8" s="66">
         <f>B7/D7</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="C8" s="68">
+      <c r="C8" s="65">
         <f>C7/D7</f>
         <v>0.55555555555555558</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="64">
         <f>SUM(B8:C8)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="66">
         <f>E7/G7</f>
         <v>0.5</v>
       </c>
-      <c r="F8" s="68">
+      <c r="F8" s="65">
         <f>F7/G7</f>
         <v>0.5</v>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="64">
         <f>SUM(E8:F8)</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="65"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="62"/>
     </row>
     <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="55">
         <f>'HRD Parameters'!B13*'HRD Budget'!B7</f>
         <v>296000</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="54">
         <f>'HRD Parameters'!C13*'HRD Budget'!C7</f>
         <v>370000</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="53">
         <f>SUM(B10:C10)</f>
         <v>666000</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="55">
         <f>E7*'HRD Parameters'!B13</f>
         <v>296000</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="54">
         <f>'HRD Parameters'!C13*'HRD Budget'!F7</f>
         <v>296000</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="53">
         <f>SUM(E10:F10)</f>
         <v>592000</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="58">
+      <c r="B11" s="55">
         <f>B5*'HRD Parameters'!B$6</f>
         <v>41000</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="54">
         <f>C5*'HRD Parameters'!C$6</f>
         <v>180000</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="53">
         <f>SUM(B11:C11)</f>
         <v>221000</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="55">
         <f>E5*'HRD Parameters'!B$6</f>
         <v>41000</v>
       </c>
-      <c r="F11" s="57">
+      <c r="F11" s="54">
         <f>F5*'HRD Parameters'!C$6</f>
         <v>180000</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="53">
         <f>SUM(E11:F11)</f>
         <v>221000</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="58">
+      <c r="B12" s="55">
         <f>'HRD Parameters'!B17*'HRD Parameters'!B19</f>
         <v>75000</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="54">
         <f>'HRD Parameters'!C17*'HRD Parameters'!C19</f>
         <v>117000</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="53">
         <f>SUM(B12:C12)</f>
         <v>192000</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="55">
         <f>'HRD Parameters'!B17*'HRD Parameters'!B19</f>
         <v>75000</v>
       </c>
-      <c r="F12" s="57">
+      <c r="F12" s="54">
         <f>'HRD Parameters'!C17*'HRD Parameters'!C19</f>
         <v>117000</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="53">
         <f>SUM(E12:F12)</f>
         <v>192000</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="55">
         <f>B5*'HRD Parameters'!B$18</f>
         <v>58000</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="54">
         <f>C5*'HRD Parameters'!C$18</f>
         <v>203500</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="53">
         <f>SUM(B13:C13)</f>
         <v>261500</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E13" s="55">
         <f>E5*'HRD Parameters'!B$18</f>
         <v>58000</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="54">
         <f>F5*'HRD Parameters'!C$18</f>
         <v>203500</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="53">
         <f>SUM(E13:F13)</f>
         <v>261500</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="55">
-        <f>SUM(B10:B13)</f>
+      <c r="B14" s="52">
+        <f t="shared" ref="B14:G14" si="0">SUM(B10:B13)</f>
         <v>470000</v>
       </c>
-      <c r="C14" s="54">
-        <f>SUM(C10:C13)</f>
+      <c r="C14" s="51">
+        <f t="shared" si="0"/>
         <v>870500</v>
       </c>
-      <c r="D14" s="53">
-        <f>SUM(D10:D13)</f>
+      <c r="D14" s="50">
+        <f t="shared" si="0"/>
         <v>1340500</v>
       </c>
-      <c r="E14" s="55">
-        <f>SUM(E10:E13)</f>
+      <c r="E14" s="52">
+        <f t="shared" si="0"/>
         <v>470000</v>
       </c>
-      <c r="F14" s="54">
-        <f>SUM(F10:F13)</f>
+      <c r="F14" s="51">
+        <f t="shared" si="0"/>
         <v>796500</v>
       </c>
-      <c r="G14" s="53">
-        <f>SUM(G10:G13)</f>
+      <c r="G14" s="50">
+        <f t="shared" si="0"/>
         <v>1266500</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="58">
-        <f>B14/B$5</f>
+      <c r="B15" s="55">
+        <f t="shared" ref="B15:G15" si="1">B14/B$5</f>
         <v>5875</v>
       </c>
-      <c r="C15" s="57">
-        <f>C14/C$5</f>
+      <c r="C15" s="54">
+        <f t="shared" si="1"/>
         <v>4705.405405405405</v>
       </c>
-      <c r="D15" s="56">
-        <f>D14/D$5</f>
+      <c r="D15" s="53">
+        <f t="shared" si="1"/>
         <v>5058.4905660377362</v>
       </c>
-      <c r="E15" s="58">
-        <f>E14/E$5</f>
+      <c r="E15" s="55">
+        <f t="shared" si="1"/>
         <v>5875</v>
       </c>
-      <c r="F15" s="57">
-        <f>F14/F$5</f>
+      <c r="F15" s="54">
+        <f t="shared" si="1"/>
         <v>4305.405405405405</v>
       </c>
-      <c r="G15" s="56">
-        <f>G14/G$5</f>
+      <c r="G15" s="53">
+        <f t="shared" si="1"/>
         <v>4779.2452830188677</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="69">
+      <c r="B16" s="66">
         <f>B14/($B14+$C14)</f>
         <v>0.35061544199925399</v>
       </c>
-      <c r="C16" s="68">
+      <c r="C16" s="65">
         <f>C14/($B14+$C14)</f>
         <v>0.64938455800074601</v>
       </c>
-      <c r="D16" s="67">
+      <c r="D16" s="64">
         <f>SUM(B16:C16)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="66">
         <f>E14/($E14+$F14)</f>
         <v>0.37110146071851557</v>
       </c>
-      <c r="F16" s="68">
+      <c r="F16" s="65">
         <f>F14/($E14+$F14)</f>
         <v>0.62889853928148443</v>
       </c>
-      <c r="G16" s="67">
+      <c r="G16" s="64">
         <f>SUM(E16:F16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="65"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="62"/>
     </row>
     <row r="18" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="58">
+      <c r="B18" s="55">
         <f>'HRD Parameters'!$D14*B8</f>
         <v>42666.666666666664</v>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="54">
         <f>'HRD Parameters'!$D14*C8</f>
         <v>53333.333333333336</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="53">
         <f>SUM(B18:C18)</f>
         <v>96000</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="55">
         <f>'HRD Parameters'!$D14*'HRD Budget'!E$8</f>
         <v>48000</v>
       </c>
-      <c r="F18" s="57">
+      <c r="F18" s="54">
         <f>'HRD Parameters'!$D14*'HRD Budget'!F$8</f>
         <v>48000</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="53">
         <f>SUM(E18:F18)</f>
         <v>96000</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="58">
+      <c r="B19" s="55">
         <f>'HRD Parameters'!$D15*B8</f>
         <v>27111.111111111109</v>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="54">
         <f>'HRD Parameters'!$D15*C8</f>
         <v>33888.888888888891</v>
       </c>
-      <c r="D19" s="56">
+      <c r="D19" s="53">
         <f>SUM(B19:C19)</f>
         <v>61000</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="55">
         <f>'HRD Parameters'!$D15*'HRD Budget'!E$8</f>
         <v>30500</v>
       </c>
-      <c r="F19" s="57">
+      <c r="F19" s="54">
         <f>'HRD Parameters'!$D15*'HRD Budget'!F$8</f>
         <v>30500</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="53">
         <f>SUM(E19:F19)</f>
         <v>61000</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="55">
         <f>'HRD Parameters'!$D20*B6</f>
         <v>63396.226415094337</v>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="54">
         <f>'HRD Parameters'!$D20*C6</f>
         <v>146603.77358490566</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="53">
         <f>SUM(B20:C20)</f>
         <v>210000</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="55">
         <f>'HRD Parameters'!$D20*E6</f>
         <v>63396.226415094337</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="54">
         <f>'HRD Parameters'!$D20*F6</f>
         <v>146603.77358490566</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="53">
         <f>SUM(E20:F20)</f>
         <v>210000</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="55">
-        <f>B18+B19+B20</f>
+      <c r="B21" s="52">
+        <f t="shared" ref="B21:G21" si="2">B18+B19+B20</f>
         <v>133174.00419287212</v>
       </c>
-      <c r="C21" s="54">
-        <f>C18+C19+C20</f>
+      <c r="C21" s="51">
+        <f t="shared" si="2"/>
         <v>233825.99580712788</v>
       </c>
-      <c r="D21" s="53">
-        <f>D18+D19+D20</f>
+      <c r="D21" s="50">
+        <f t="shared" si="2"/>
         <v>367000</v>
       </c>
-      <c r="E21" s="55">
-        <f>E18+E19+E20</f>
+      <c r="E21" s="52">
+        <f t="shared" si="2"/>
         <v>141896.22641509434</v>
       </c>
-      <c r="F21" s="54">
-        <f>F18+F19+F20</f>
+      <c r="F21" s="51">
+        <f t="shared" si="2"/>
         <v>225103.77358490566</v>
       </c>
-      <c r="G21" s="53">
-        <f>G18+G19+G20</f>
+      <c r="G21" s="50">
+        <f t="shared" si="2"/>
         <v>367000</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="64">
-        <f>B21/B$5</f>
+      <c r="B22" s="61">
+        <f t="shared" ref="B22:G22" si="3">B21/B$5</f>
         <v>1664.6750524109016</v>
       </c>
-      <c r="C22" s="63">
-        <f>C21/C$5</f>
+      <c r="C22" s="60">
+        <f t="shared" si="3"/>
         <v>1263.9243016601506</v>
       </c>
-      <c r="D22" s="62">
-        <f>D21/D$5</f>
+      <c r="D22" s="59">
+        <f t="shared" si="3"/>
         <v>1384.9056603773586</v>
       </c>
-      <c r="E22" s="64">
-        <f>E21/E$5</f>
+      <c r="E22" s="61">
+        <f t="shared" si="3"/>
         <v>1773.7028301886792</v>
       </c>
-      <c r="F22" s="63">
-        <f>F21/F$5</f>
+      <c r="F22" s="60">
+        <f t="shared" si="3"/>
         <v>1216.7771545130036</v>
       </c>
-      <c r="G22" s="62">
-        <f>G21/G$5</f>
+      <c r="G22" s="59">
+        <f t="shared" si="3"/>
         <v>1384.9056603773586</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="55">
-        <f>B21+B14</f>
+      <c r="B23" s="52">
+        <f t="shared" ref="B23:G23" si="4">B21+B14</f>
         <v>603174.00419287209</v>
       </c>
-      <c r="C23" s="54">
-        <f>C21+C14</f>
+      <c r="C23" s="51">
+        <f t="shared" si="4"/>
         <v>1104325.9958071278</v>
       </c>
-      <c r="D23" s="53">
-        <f>D21+D14</f>
+      <c r="D23" s="50">
+        <f t="shared" si="4"/>
         <v>1707500</v>
       </c>
-      <c r="E23" s="55">
-        <f>E21+E14</f>
+      <c r="E23" s="52">
+        <f t="shared" si="4"/>
         <v>611896.22641509434</v>
       </c>
-      <c r="F23" s="54">
-        <f>F21+F14</f>
+      <c r="F23" s="51">
+        <f t="shared" si="4"/>
         <v>1021603.7735849057</v>
       </c>
-      <c r="G23" s="53">
-        <f>G21+G14</f>
+      <c r="G23" s="50">
+        <f t="shared" si="4"/>
         <v>1633500</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="58">
-        <f>B23/B$5</f>
+      <c r="B24" s="55">
+        <f t="shared" ref="B24:G24" si="5">B23/B$5</f>
         <v>7539.6750524109011</v>
       </c>
-      <c r="C24" s="57">
-        <f>C23/C$5</f>
+      <c r="C24" s="54">
+        <f t="shared" si="5"/>
         <v>5969.3297070655553</v>
       </c>
-      <c r="D24" s="56">
-        <f>D23/D$5</f>
+      <c r="D24" s="53">
+        <f t="shared" si="5"/>
         <v>6443.3962264150941</v>
       </c>
-      <c r="E24" s="58">
-        <f>E23/E$5</f>
+      <c r="E24" s="55">
+        <f t="shared" si="5"/>
         <v>7648.7028301886794</v>
       </c>
-      <c r="F24" s="57">
-        <f>F23/F$5</f>
+      <c r="F24" s="54">
+        <f t="shared" si="5"/>
         <v>5522.1825599184094</v>
       </c>
-      <c r="G24" s="56">
-        <f>G23/G$5</f>
+      <c r="G24" s="53">
+        <f t="shared" si="5"/>
         <v>6164.1509433962265</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="55">
         <f>B5*'HRD Parameters'!B9</f>
         <v>500000</v>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="54">
         <f>C5*'HRD Parameters'!C9</f>
         <v>1887000</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D25" s="53">
         <f>SUM(B25:C25)</f>
         <v>2387000</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="52">
         <f>E5*'HRD Parameters'!B9</f>
         <v>500000</v>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="51">
         <f>F5*'HRD Parameters'!C9</f>
         <v>1887000</v>
       </c>
-      <c r="G25" s="53">
+      <c r="G25" s="50">
         <f>SUM(E25:F25)</f>
         <v>2387000</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="58">
-        <f>+B25-B23</f>
+      <c r="B26" s="55">
+        <f t="shared" ref="B26:G26" si="6">+B25-B23</f>
         <v>-103174.00419287209</v>
       </c>
-      <c r="C26" s="57">
-        <f>+C25-C23</f>
+      <c r="C26" s="54">
+        <f t="shared" si="6"/>
         <v>782674.00419287221</v>
       </c>
-      <c r="D26" s="56">
-        <f>+D25-D23</f>
+      <c r="D26" s="53">
+        <f t="shared" si="6"/>
         <v>679500</v>
       </c>
-      <c r="E26" s="55">
-        <f>+E25-E23</f>
+      <c r="E26" s="52">
+        <f t="shared" si="6"/>
         <v>-111896.22641509434</v>
       </c>
-      <c r="F26" s="54">
-        <f>+F25-F23</f>
+      <c r="F26" s="51">
+        <f t="shared" si="6"/>
         <v>865396.22641509434</v>
       </c>
-      <c r="G26" s="53">
-        <f>+G25-G23</f>
+      <c r="G26" s="50">
+        <f t="shared" si="6"/>
         <v>753500</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="52" t="s">
+      <c r="A27" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="51">
-        <f>+B26/B5</f>
+      <c r="B27" s="48">
+        <f t="shared" ref="B27:G27" si="7">+B26/B5</f>
         <v>-1289.6750524109011</v>
       </c>
-      <c r="C27" s="50">
-        <f>+C26/C5</f>
+      <c r="C27" s="47">
+        <f t="shared" si="7"/>
         <v>4230.6702929344447</v>
       </c>
-      <c r="D27" s="49">
-        <f>+D26/D5</f>
+      <c r="D27" s="46">
+        <f t="shared" si="7"/>
         <v>2564.1509433962265</v>
       </c>
-      <c r="E27" s="51">
-        <f>+E26/E5</f>
+      <c r="E27" s="48">
+        <f t="shared" si="7"/>
         <v>-1398.7028301886792</v>
       </c>
-      <c r="F27" s="50">
-        <f>+F26/F5</f>
+      <c r="F27" s="47">
+        <f t="shared" si="7"/>
         <v>4677.8174400815906</v>
       </c>
-      <c r="G27" s="49">
-        <f>+G26/G5</f>
+      <c r="G27" s="46">
+        <f t="shared" si="7"/>
         <v>2843.3962264150941</v>
       </c>
     </row>
@@ -3515,1102 +3832,1102 @@
   <dimension ref="A1:G75"/>
   <sheetFormatPr defaultColWidth="15.69140625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.69140625" style="93"/>
-    <col min="2" max="16384" width="15.69140625" style="92"/>
+    <col min="1" max="1" width="15.69140625" style="84"/>
+    <col min="2" max="16384" width="15.69140625" style="83"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="96" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="115" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="118"/>
+      <c r="D2" s="117"/>
       <c r="E2" s="119" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="118">
+      <c r="F2" s="117">
         <v>2018</v>
       </c>
-      <c r="G2" s="118"/>
+      <c r="G2" s="117"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="117"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="114" t="s">
+      <c r="A3" s="116"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="114" t="s">
+      <c r="D3" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="115"/>
-      <c r="F3" s="114" t="s">
+      <c r="E3" s="120"/>
+      <c r="F3" s="105" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="114" t="s">
+      <c r="G3" s="105" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="83">
         <v>0.6</v>
       </c>
-      <c r="C4" s="113">
+      <c r="C4" s="104">
         <v>74720</v>
       </c>
-      <c r="D4" s="113">
+      <c r="D4" s="104">
         <v>78652</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="83">
         <v>8</v>
       </c>
-      <c r="F4" s="92">
+      <c r="F4" s="83">
         <v>8</v>
       </c>
-      <c r="G4" s="92">
+      <c r="G4" s="83">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="83">
         <v>0.5</v>
       </c>
-      <c r="C5" s="113">
+      <c r="C5" s="104">
         <v>65309</v>
       </c>
-      <c r="D5" s="113">
+      <c r="D5" s="104">
         <v>68747</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="83">
         <v>20</v>
       </c>
-      <c r="F5" s="92">
+      <c r="F5" s="83">
         <v>20</v>
       </c>
-      <c r="G5" s="92">
+      <c r="G5" s="83">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="109">
+      <c r="B6" s="100">
         <v>0.4</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="103">
         <v>44467</v>
       </c>
-      <c r="D6" s="112">
+      <c r="D6" s="103">
         <v>63297</v>
       </c>
-      <c r="E6" s="109">
+      <c r="E6" s="100">
         <v>119</v>
       </c>
-      <c r="F6" s="109">
+      <c r="F6" s="100">
         <v>119</v>
       </c>
-      <c r="G6" s="109">
+      <c r="G6" s="100">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="105" t="s">
+      <c r="A8" s="96" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="94" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="94" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="D9" s="94" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="94" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="103" t="s">
+      <c r="F9" s="94" t="s">
         <v>129</v>
       </c>
-      <c r="G9" s="103" t="s">
+      <c r="G9" s="94" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="93" t="s">
+      <c r="A10" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="100">
+      <c r="B10" s="91">
         <v>10</v>
       </c>
-      <c r="C10" s="100">
+      <c r="C10" s="91">
         <v>20</v>
       </c>
-      <c r="D10" s="100">
+      <c r="D10" s="91">
         <v>20</v>
       </c>
-      <c r="E10" s="100">
+      <c r="E10" s="91">
         <v>30</v>
       </c>
-      <c r="F10" s="100">
+      <c r="F10" s="91">
         <v>39</v>
       </c>
-      <c r="G10" s="100">
+      <c r="G10" s="91">
         <f>SUM(B10:F10)</f>
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="102"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="100" t="s">
+      <c r="C11" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="100" t="s">
+      <c r="D11" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="100"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="100">
+      <c r="B12" s="91">
         <v>2</v>
       </c>
-      <c r="C12" s="100">
+      <c r="C12" s="91">
         <v>6</v>
       </c>
-      <c r="D12" s="100">
+      <c r="D12" s="91">
         <f>SUM(B12:C12)</f>
         <v>8</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="100"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="99" t="s">
+      <c r="A13" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="97">
+      <c r="B13" s="88">
         <v>6</v>
       </c>
-      <c r="C13" s="97">
+      <c r="C13" s="88">
         <v>14</v>
       </c>
-      <c r="D13" s="97">
+      <c r="D13" s="88">
         <f>SUM(B13:C13)</f>
         <v>20</v>
       </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="87" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="105" t="s">
+      <c r="A16" s="96" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="103" t="str">
+      <c r="B17" s="94" t="str">
         <f>B9</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C17" s="103" t="str">
+      <c r="C17" s="94" t="str">
         <f>C9</f>
         <v>1 year</v>
       </c>
-      <c r="D17" s="103" t="str">
+      <c r="D17" s="94" t="str">
         <f>D9</f>
         <v>2 years</v>
       </c>
-      <c r="E17" s="103" t="str">
+      <c r="E17" s="94" t="str">
         <f>E9</f>
         <v>3 years</v>
       </c>
-      <c r="F17" s="103" t="str">
+      <c r="F17" s="94" t="str">
         <f>F9</f>
         <v>4 and more years</v>
       </c>
-      <c r="G17" s="103" t="s">
+      <c r="G17" s="94" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="93" t="s">
+      <c r="A18" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="100">
+      <c r="B18" s="91">
         <v>0</v>
       </c>
-      <c r="C18" s="100">
+      <c r="C18" s="91">
         <v>10</v>
       </c>
-      <c r="D18" s="100">
+      <c r="D18" s="91">
         <v>20</v>
       </c>
-      <c r="E18" s="100">
+      <c r="E18" s="91">
         <v>20</v>
       </c>
-      <c r="F18" s="100">
+      <c r="F18" s="91">
         <v>69</v>
       </c>
-      <c r="G18" s="100">
+      <c r="G18" s="91">
         <f>SUM(B18:F18)</f>
         <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="102"/>
-      <c r="B19" s="100" t="s">
+      <c r="A19" s="93"/>
+      <c r="B19" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="100" t="s">
+      <c r="D19" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="93" t="s">
+      <c r="A20" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="100">
+      <c r="B20" s="91">
         <v>0</v>
       </c>
-      <c r="C20" s="100">
+      <c r="C20" s="91">
         <v>8</v>
       </c>
-      <c r="D20" s="100">
+      <c r="D20" s="91">
         <f>SUM(B20:C20)</f>
         <v>8</v>
       </c>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="97">
+      <c r="B21" s="88">
         <v>0</v>
       </c>
-      <c r="C21" s="97">
+      <c r="C21" s="88">
         <v>20</v>
       </c>
-      <c r="D21" s="97">
+      <c r="D21" s="88">
         <f>SUM(B21:C21)</f>
         <v>20</v>
       </c>
-      <c r="E21" s="97"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="100"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="100"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="G23" s="100"/>
+      <c r="G23" s="91"/>
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="104" t="s">
+      <c r="A24" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="103" t="str">
+      <c r="B24" s="94" t="str">
         <f>B17</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C24" s="103" t="str">
+      <c r="C24" s="94" t="str">
         <f>C17</f>
         <v>1 year</v>
       </c>
-      <c r="D24" s="103" t="str">
+      <c r="D24" s="94" t="str">
         <f>D17</f>
         <v>2 years</v>
       </c>
-      <c r="E24" s="103" t="str">
+      <c r="E24" s="94" t="str">
         <f>E17</f>
         <v>3 years</v>
       </c>
-      <c r="F24" s="103" t="str">
+      <c r="F24" s="94" t="str">
         <f>F17</f>
         <v>4 and more years</v>
       </c>
-      <c r="G24" s="100"/>
+      <c r="G24" s="91"/>
     </row>
     <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="93" t="s">
+      <c r="A25" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="101">
+      <c r="B25" s="92">
         <v>46718</v>
       </c>
-      <c r="C25" s="101">
+      <c r="C25" s="92">
         <v>54033</v>
       </c>
-      <c r="D25" s="101">
+      <c r="D25" s="92">
         <v>55801</v>
       </c>
-      <c r="E25" s="101">
+      <c r="E25" s="92">
         <v>57632</v>
       </c>
-      <c r="F25" s="101">
+      <c r="F25" s="92">
         <v>66501</v>
       </c>
-      <c r="G25" s="100"/>
+      <c r="G25" s="91"/>
     </row>
     <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="102"/>
-      <c r="B26" s="100" t="s">
+      <c r="A26" s="93"/>
+      <c r="B26" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="100"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="91"/>
     </row>
     <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="101">
+      <c r="B27" s="92">
         <v>80465</v>
       </c>
-      <c r="C27" s="101">
+      <c r="C27" s="92">
         <v>84700</v>
       </c>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="98">
+      <c r="B28" s="89">
         <v>70331</v>
       </c>
-      <c r="C28" s="98">
+      <c r="C28" s="89">
         <v>75033</v>
       </c>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="100"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="91"/>
     </row>
     <row r="29" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="G29" s="100"/>
+      <c r="G29" s="91"/>
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="G30" s="100"/>
+      <c r="G30" s="91"/>
     </row>
     <row r="31" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="104" t="s">
+      <c r="A31" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="103" t="str">
+      <c r="B31" s="94" t="str">
         <f>B24</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C31" s="103" t="str">
+      <c r="C31" s="94" t="str">
         <f>C24</f>
         <v>1 year</v>
       </c>
-      <c r="D31" s="103" t="str">
+      <c r="D31" s="94" t="str">
         <f>D24</f>
         <v>2 years</v>
       </c>
-      <c r="E31" s="103" t="str">
+      <c r="E31" s="94" t="str">
         <f>E24</f>
         <v>3 years</v>
       </c>
-      <c r="F31" s="103" t="str">
+      <c r="F31" s="94" t="str">
         <f>F24</f>
         <v>4 and more years</v>
       </c>
-      <c r="G31" s="100"/>
+      <c r="G31" s="91"/>
     </row>
     <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="93" t="s">
+      <c r="A32" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="101">
+      <c r="B32" s="92">
         <f>B25*B18</f>
         <v>0</v>
       </c>
-      <c r="C32" s="101">
+      <c r="C32" s="92">
         <f>C25*C18</f>
         <v>540330</v>
       </c>
-      <c r="D32" s="101">
+      <c r="D32" s="92">
         <f>D25*D18</f>
         <v>1116020</v>
       </c>
-      <c r="E32" s="101">
+      <c r="E32" s="92">
         <f>E25*E18</f>
         <v>1152640</v>
       </c>
-      <c r="F32" s="101">
+      <c r="F32" s="92">
         <f>F25*F18</f>
         <v>4588569</v>
       </c>
-      <c r="G32" s="100"/>
+      <c r="G32" s="91"/>
     </row>
     <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="102"/>
-      <c r="B33" s="100" t="s">
+      <c r="A33" s="93"/>
+      <c r="B33" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="100" t="s">
+      <c r="C33" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="100"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
     </row>
     <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="93" t="s">
+      <c r="A34" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="101">
+      <c r="B34" s="92">
         <f>B27*B20</f>
         <v>0</v>
       </c>
-      <c r="C34" s="101">
+      <c r="C34" s="92">
         <f>C27*C20</f>
         <v>677600</v>
       </c>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="91"/>
     </row>
     <row r="35" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="99" t="s">
+      <c r="A35" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="98">
+      <c r="B35" s="89">
         <f>B21*B28</f>
         <v>0</v>
       </c>
-      <c r="C35" s="98">
+      <c r="C35" s="89">
         <f>C21*C28</f>
         <v>1500660</v>
       </c>
-      <c r="D35" s="97"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="100"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="91"/>
     </row>
     <row r="36" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="100"/>
-      <c r="C36" s="100"/>
-      <c r="D36" s="100"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="91"/>
     </row>
     <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="96" t="s">
+      <c r="A37" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="95"/>
-      <c r="C37" s="94">
+      <c r="B37" s="86"/>
+      <c r="C37" s="85">
         <f>SUM(B32:F32)+SUM(B34:C35)</f>
         <v>9575819</v>
       </c>
-      <c r="D37" s="100"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="100"/>
-      <c r="G37" s="100"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="91"/>
     </row>
     <row r="39" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="96" t="s">
+      <c r="A39" s="87" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="105" t="s">
+      <c r="A40" s="96" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="104" t="s">
+      <c r="A41" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="103" t="str">
+      <c r="B41" s="94" t="str">
         <f>B17</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C41" s="103" t="str">
+      <c r="C41" s="94" t="str">
         <f>C17</f>
         <v>1 year</v>
       </c>
-      <c r="D41" s="103" t="str">
+      <c r="D41" s="94" t="str">
         <f>D17</f>
         <v>2 years</v>
       </c>
-      <c r="E41" s="103" t="str">
+      <c r="E41" s="94" t="str">
         <f>E17</f>
         <v>3 years</v>
       </c>
-      <c r="F41" s="103" t="str">
+      <c r="F41" s="94" t="str">
         <f>F17</f>
         <v>4 and more years</v>
       </c>
-      <c r="G41" s="106"/>
+      <c r="G41" s="97"/>
     </row>
     <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="93" t="s">
+      <c r="A42" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="111">
+      <c r="B42" s="102">
         <v>0.1</v>
       </c>
-      <c r="C42" s="111">
+      <c r="C42" s="102">
         <v>0.08</v>
       </c>
-      <c r="D42" s="111">
+      <c r="D42" s="102">
         <v>0.08</v>
       </c>
-      <c r="E42" s="111">
+      <c r="E42" s="102">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F42" s="111">
+      <c r="F42" s="102">
         <v>0.1</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="102"/>
-      <c r="B43" s="100" t="s">
+      <c r="A43" s="93"/>
+      <c r="B43" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="100" t="s">
+      <c r="C43" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D43" s="100"/>
+      <c r="D43" s="91"/>
     </row>
     <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="111">
+      <c r="B44" s="102">
         <v>0.05</v>
       </c>
-      <c r="C44" s="111">
+      <c r="C44" s="102">
         <v>0.1</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="99" t="s">
+      <c r="A45" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B45" s="110">
+      <c r="B45" s="101">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C45" s="110">
+      <c r="C45" s="101">
         <v>0.05</v>
       </c>
-      <c r="D45" s="109"/>
-      <c r="E45" s="109"/>
-      <c r="F45" s="109"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
     </row>
     <row r="46" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="105" t="s">
+      <c r="A47" s="96" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="104" t="s">
+      <c r="A48" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B48" s="103" t="str">
+      <c r="B48" s="94" t="str">
         <f>B41</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C48" s="103" t="str">
+      <c r="C48" s="94" t="str">
         <f>C41</f>
         <v>1 year</v>
       </c>
-      <c r="D48" s="103" t="str">
+      <c r="D48" s="94" t="str">
         <f>D41</f>
         <v>2 years</v>
       </c>
-      <c r="E48" s="103" t="str">
+      <c r="E48" s="94" t="str">
         <f>E41</f>
         <v>3 years</v>
       </c>
-      <c r="F48" s="103" t="str">
+      <c r="F48" s="94" t="str">
         <f>F41</f>
         <v>4 and more years</v>
       </c>
-      <c r="G48" s="103" t="s">
+      <c r="G48" s="94" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="108" t="s">
+      <c r="A49" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="107">
+      <c r="B49" s="98">
         <f>ROUNDUP(B42*B10,0)</f>
         <v>1</v>
       </c>
-      <c r="C49" s="107">
+      <c r="C49" s="98">
         <f>ROUNDUP(C42*C10,0)</f>
         <v>2</v>
       </c>
-      <c r="D49" s="107">
+      <c r="D49" s="98">
         <f>ROUNDUP(D42*D10,0)</f>
         <v>2</v>
       </c>
-      <c r="E49" s="107">
+      <c r="E49" s="98">
         <f>ROUNDUP(E42*E10,0)</f>
         <v>3</v>
       </c>
-      <c r="F49" s="107">
+      <c r="F49" s="98">
         <f>ROUNDUP(F42*F10,0)</f>
         <v>4</v>
       </c>
-      <c r="G49" s="107">
+      <c r="G49" s="98">
         <f>SUM(B49:F49)</f>
         <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="102"/>
-      <c r="B50" s="100" t="s">
+      <c r="A50" s="93"/>
+      <c r="B50" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="100" t="s">
+      <c r="C50" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D50" s="100" t="s">
+      <c r="D50" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="100"/>
-      <c r="F50" s="100"/>
-      <c r="G50" s="100"/>
+      <c r="E50" s="91"/>
+      <c r="F50" s="91"/>
+      <c r="G50" s="91"/>
     </row>
     <row r="51" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="93" t="s">
+      <c r="A51" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="100">
+      <c r="B51" s="91">
         <f>ROUNDUP(B44*B12,0)</f>
         <v>1</v>
       </c>
-      <c r="C51" s="100">
+      <c r="C51" s="91">
         <f>ROUNDUP(C44*C12,0)</f>
         <v>1</v>
       </c>
-      <c r="D51" s="100">
+      <c r="D51" s="91">
         <f>SUM(B51:C51)</f>
         <v>2</v>
       </c>
-      <c r="E51" s="100"/>
-      <c r="F51" s="100"/>
-      <c r="G51" s="100"/>
+      <c r="E51" s="91"/>
+      <c r="F51" s="91"/>
+      <c r="G51" s="91"/>
     </row>
     <row r="52" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="99" t="s">
+      <c r="A52" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="97">
+      <c r="B52" s="88">
         <f>ROUNDUP(B45*B13,0)</f>
         <v>1</v>
       </c>
-      <c r="C52" s="97">
+      <c r="C52" s="88">
         <f>ROUNDUP(C45*C13,0)</f>
         <v>1</v>
       </c>
-      <c r="D52" s="97">
+      <c r="D52" s="88">
         <f>SUM(B52:C52)</f>
         <v>2</v>
       </c>
-      <c r="E52" s="97"/>
-      <c r="F52" s="97"/>
-      <c r="G52" s="97"/>
+      <c r="E52" s="88"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="88"/>
     </row>
     <row r="53" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="105" t="s">
+      <c r="A54" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="104" t="s">
+      <c r="A55" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="103" t="str">
+      <c r="B55" s="94" t="str">
         <f>B48</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C55" s="103" t="str">
+      <c r="C55" s="94" t="str">
         <f>C48</f>
         <v>1 year</v>
       </c>
-      <c r="D55" s="103" t="str">
+      <c r="D55" s="94" t="str">
         <f>D48</f>
         <v>2 years</v>
       </c>
-      <c r="E55" s="103" t="str">
+      <c r="E55" s="94" t="str">
         <f>E48</f>
         <v>3 years</v>
       </c>
-      <c r="F55" s="103" t="str">
+      <c r="F55" s="94" t="str">
         <f>F48</f>
         <v>4 and more years</v>
       </c>
-      <c r="G55" s="103" t="s">
+      <c r="G55" s="94" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="93" t="s">
+      <c r="A56" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B56" s="100">
+      <c r="B56" s="91">
         <f>G49</f>
         <v>12</v>
       </c>
-      <c r="C56" s="100">
+      <c r="C56" s="91">
         <f>B10-B49</f>
         <v>9</v>
       </c>
-      <c r="D56" s="100">
+      <c r="D56" s="91">
         <f>C10-C49</f>
         <v>18</v>
       </c>
-      <c r="E56" s="100">
+      <c r="E56" s="91">
         <f>D10-D49</f>
         <v>18</v>
       </c>
-      <c r="F56" s="100">
+      <c r="F56" s="91">
         <f>F10-F49+E10-E49</f>
         <v>62</v>
       </c>
-      <c r="G56" s="100">
+      <c r="G56" s="91">
         <f>SUM(B56:F56)</f>
         <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="102"/>
-      <c r="B57" s="100" t="s">
+      <c r="A57" s="93"/>
+      <c r="B57" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="100" t="s">
+      <c r="C57" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="100" t="s">
+      <c r="D57" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="100"/>
-      <c r="F57" s="100"/>
-      <c r="G57" s="100"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="91"/>
     </row>
     <row r="58" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="93" t="s">
+      <c r="A58" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B58" s="100">
+      <c r="B58" s="91">
         <f>D51</f>
         <v>2</v>
       </c>
-      <c r="C58" s="100">
+      <c r="C58" s="91">
         <f>C12-C51+B12-B51</f>
         <v>6</v>
       </c>
-      <c r="D58" s="100">
+      <c r="D58" s="91">
         <f>SUM(B58:C58)</f>
         <v>8</v>
       </c>
-      <c r="E58" s="100"/>
-      <c r="F58" s="100"/>
-      <c r="G58" s="100"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="91"/>
     </row>
     <row r="59" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="99" t="s">
+      <c r="A59" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="97">
+      <c r="B59" s="88">
         <f>D52</f>
         <v>2</v>
       </c>
-      <c r="C59" s="97">
+      <c r="C59" s="88">
         <f>C13-C52+B13-B52</f>
         <v>18</v>
       </c>
-      <c r="D59" s="97">
+      <c r="D59" s="88">
         <f>SUM(B59:C59)</f>
         <v>20</v>
       </c>
-      <c r="E59" s="97"/>
-      <c r="F59" s="97"/>
-      <c r="G59" s="97"/>
+      <c r="E59" s="88"/>
+      <c r="F59" s="88"/>
+      <c r="G59" s="88"/>
     </row>
     <row r="60" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="61" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="105" t="s">
+      <c r="A61" s="96" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="104" t="s">
+      <c r="A62" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="103" t="str">
+      <c r="B62" s="94" t="str">
         <f>B55</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C62" s="103" t="str">
+      <c r="C62" s="94" t="str">
         <f>C55</f>
         <v>1 year</v>
       </c>
-      <c r="D62" s="103" t="str">
+      <c r="D62" s="94" t="str">
         <f>D55</f>
         <v>2 years</v>
       </c>
-      <c r="E62" s="103" t="str">
+      <c r="E62" s="94" t="str">
         <f>E55</f>
         <v>3 years</v>
       </c>
-      <c r="F62" s="103" t="str">
+      <c r="F62" s="94" t="str">
         <f>F55</f>
         <v>4 and more years</v>
       </c>
-      <c r="G62" s="106"/>
+      <c r="G62" s="97"/>
     </row>
     <row r="63" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="93" t="s">
+      <c r="A63" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B63" s="101">
+      <c r="B63" s="92">
         <v>46718</v>
       </c>
-      <c r="C63" s="101">
+      <c r="C63" s="92">
         <v>54033</v>
       </c>
-      <c r="D63" s="101">
+      <c r="D63" s="92">
         <v>55801</v>
       </c>
-      <c r="E63" s="101">
+      <c r="E63" s="92">
         <v>57632</v>
       </c>
-      <c r="F63" s="101">
+      <c r="F63" s="92">
         <v>66501</v>
       </c>
-      <c r="G63" s="100"/>
+      <c r="G63" s="91"/>
     </row>
     <row r="64" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="102"/>
-      <c r="B64" s="100" t="s">
+      <c r="A64" s="93"/>
+      <c r="B64" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C64" s="100" t="s">
+      <c r="C64" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D64" s="100"/>
-      <c r="E64" s="100"/>
-      <c r="F64" s="100"/>
-      <c r="G64" s="100"/>
+      <c r="D64" s="91"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="91"/>
     </row>
     <row r="65" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="93" t="s">
+      <c r="A65" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B65" s="101">
+      <c r="B65" s="92">
         <v>80465</v>
       </c>
-      <c r="C65" s="101">
+      <c r="C65" s="92">
         <v>84700</v>
       </c>
-      <c r="D65" s="100"/>
-      <c r="E65" s="100"/>
-      <c r="F65" s="100"/>
-      <c r="G65" s="100"/>
+      <c r="D65" s="91"/>
+      <c r="E65" s="91"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="91"/>
     </row>
     <row r="66" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="99" t="s">
+      <c r="A66" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B66" s="98">
+      <c r="B66" s="89">
         <v>70331</v>
       </c>
-      <c r="C66" s="98">
+      <c r="C66" s="89">
         <v>75033</v>
       </c>
-      <c r="D66" s="97"/>
-      <c r="E66" s="97"/>
-      <c r="F66" s="97"/>
-      <c r="G66" s="100"/>
+      <c r="D66" s="88"/>
+      <c r="E66" s="88"/>
+      <c r="F66" s="88"/>
+      <c r="G66" s="91"/>
     </row>
     <row r="67" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="68" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A68" s="105" t="s">
+      <c r="A68" s="96" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="104" t="s">
+      <c r="A69" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B69" s="103" t="str">
+      <c r="B69" s="94" t="str">
         <f>B62</f>
         <v>&lt; 1 year</v>
       </c>
-      <c r="C69" s="103" t="str">
+      <c r="C69" s="94" t="str">
         <f>C62</f>
         <v>1 year</v>
       </c>
-      <c r="D69" s="103" t="str">
+      <c r="D69" s="94" t="str">
         <f>D62</f>
         <v>2 years</v>
       </c>
-      <c r="E69" s="103" t="str">
+      <c r="E69" s="94" t="str">
         <f>E62</f>
         <v>3 years</v>
       </c>
-      <c r="F69" s="103" t="str">
+      <c r="F69" s="94" t="str">
         <f>F62</f>
         <v>4 and more years</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="93" t="s">
+      <c r="A70" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B70" s="101">
+      <c r="B70" s="92">
         <f>B63*B56</f>
         <v>560616</v>
       </c>
-      <c r="C70" s="101">
+      <c r="C70" s="92">
         <f>C63*C56</f>
         <v>486297</v>
       </c>
-      <c r="D70" s="101">
+      <c r="D70" s="92">
         <f>D63*D56</f>
         <v>1004418</v>
       </c>
-      <c r="E70" s="101">
+      <c r="E70" s="92">
         <f>E63*E56</f>
         <v>1037376</v>
       </c>
-      <c r="F70" s="101">
+      <c r="F70" s="92">
         <f>F63*F56</f>
         <v>4123062</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="102"/>
-      <c r="B71" s="100" t="s">
+      <c r="A71" s="93"/>
+      <c r="B71" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="C71" s="100" t="s">
+      <c r="C71" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="D71" s="100"/>
-      <c r="E71" s="100"/>
-      <c r="F71" s="100"/>
+      <c r="D71" s="91"/>
+      <c r="E71" s="91"/>
+      <c r="F71" s="91"/>
     </row>
     <row r="72" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="93" t="s">
+      <c r="A72" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B72" s="101">
+      <c r="B72" s="92">
         <f>B65*B58</f>
         <v>160930</v>
       </c>
-      <c r="C72" s="101">
+      <c r="C72" s="92">
         <f>C65*C58</f>
         <v>508200</v>
       </c>
-      <c r="D72" s="100"/>
-      <c r="E72" s="100"/>
-      <c r="F72" s="100"/>
+      <c r="D72" s="91"/>
+      <c r="E72" s="91"/>
+      <c r="F72" s="91"/>
     </row>
     <row r="73" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="99" t="s">
+      <c r="A73" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="B73" s="98">
+      <c r="B73" s="89">
         <f>B66*B59</f>
         <v>140662</v>
       </c>
-      <c r="C73" s="98">
+      <c r="C73" s="89">
         <f>C66*C59</f>
         <v>1350594</v>
       </c>
-      <c r="D73" s="97"/>
-      <c r="E73" s="97"/>
-      <c r="F73" s="97"/>
+      <c r="D73" s="88"/>
+      <c r="E73" s="88"/>
+      <c r="F73" s="88"/>
     </row>
     <row r="74" spans="1:7" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="75" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="96" t="s">
+      <c r="A75" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="B75" s="95"/>
-      <c r="C75" s="94">
+      <c r="B75" s="86"/>
+      <c r="C75" s="85">
         <f>SUM(B70:F70)+SUM(B72:C73)</f>
         <v>9372155</v>
       </c>
@@ -4629,4 +4946,814 @@
     <brk id="37" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC87D1C8-7C82-4FC1-87F6-F4BFE6138817}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="21.765625" defaultRowHeight="20.05" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.765625" style="1"/>
+    <col min="2" max="2" width="23.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="21.765625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="145">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="144">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="10">
+        <f>B5*B8+B6*B8^2</f>
+        <v>64500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="143">
+        <f>B9/B2</f>
+        <v>0.64500000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="142">
+        <f>B3*LN(B8)-B4*B2/B8</f>
+        <v>-9543.6974020275047</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="142">
+        <f>B2*B12-B9</f>
+        <v>-954434240.20275044</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51E47AF-D6D0-469D-9141-1FE557419960}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="40.69140625" style="122" customWidth="1"/>
+    <col min="2" max="11" width="15.69140625" style="122" customWidth="1"/>
+    <col min="12" max="12" width="15.69140625" style="125" customWidth="1"/>
+    <col min="13" max="16384" width="9.15234375" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="121" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+    </row>
+    <row r="2" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="123" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="124" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="124" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="124" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="124" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="124" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="124" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="124" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" s="124" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="124" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2" s="124" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="122" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="122">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="122">
+        <f>B3-0.03</f>
+        <v>0.47</v>
+      </c>
+      <c r="D3" s="122">
+        <f t="shared" ref="D3:K3" si="0">C3-0.03</f>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="E3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.40999999999999992</v>
+      </c>
+      <c r="F3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.37999999999999989</v>
+      </c>
+      <c r="G3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.34999999999999987</v>
+      </c>
+      <c r="H3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.31999999999999984</v>
+      </c>
+      <c r="I3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.28999999999999981</v>
+      </c>
+      <c r="J3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.25999999999999979</v>
+      </c>
+      <c r="K3" s="122">
+        <f t="shared" si="0"/>
+        <v>0.22999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="122" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="122">
+        <v>0.4</v>
+      </c>
+      <c r="C4" s="122">
+        <f>B4-0.01</f>
+        <v>0.39</v>
+      </c>
+      <c r="D4" s="122">
+        <f t="shared" ref="D4:K4" si="1">C4-0.01</f>
+        <v>0.38</v>
+      </c>
+      <c r="E4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="F4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.36</v>
+      </c>
+      <c r="G4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="H4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="I4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="J4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.31999999999999995</v>
+      </c>
+      <c r="K4" s="122">
+        <f t="shared" si="1"/>
+        <v>0.30999999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="122">
+        <f>1-B4-B3</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="C5" s="122">
+        <f t="shared" ref="C5:K5" si="2">1-C4-C3</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.18000000000000005</v>
+      </c>
+      <c r="E5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.22000000000000008</v>
+      </c>
+      <c r="F5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.26000000000000012</v>
+      </c>
+      <c r="G5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.30000000000000016</v>
+      </c>
+      <c r="H5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.34000000000000019</v>
+      </c>
+      <c r="I5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.38000000000000023</v>
+      </c>
+      <c r="J5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.42000000000000026</v>
+      </c>
+      <c r="K5" s="122">
+        <f t="shared" si="2"/>
+        <v>0.4600000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="122" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="126">
+        <v>7000</v>
+      </c>
+      <c r="C6" s="126">
+        <v>20000</v>
+      </c>
+      <c r="D6" s="126">
+        <v>30000</v>
+      </c>
+      <c r="E6" s="126">
+        <v>41000</v>
+      </c>
+      <c r="F6" s="126">
+        <v>54000</v>
+      </c>
+      <c r="G6" s="126">
+        <v>70000</v>
+      </c>
+      <c r="H6" s="126">
+        <v>90000</v>
+      </c>
+      <c r="I6" s="126">
+        <v>115000</v>
+      </c>
+      <c r="J6" s="126">
+        <v>155000</v>
+      </c>
+      <c r="K6" s="126">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="122" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="D7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="E7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="F7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="G7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="I7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="J7" s="127">
+        <v>0.03</v>
+      </c>
+      <c r="K7" s="127">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="122" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="I8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="J8" s="127">
+        <v>0.05</v>
+      </c>
+      <c r="K8" s="127">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="122" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+    </row>
+    <row r="10" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="122" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="128"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+    </row>
+    <row r="11" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="122" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+    </row>
+    <row r="12" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="129" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+    </row>
+    <row r="13" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="122" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="131">
+        <f>SUM(B13:K13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="129" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+    </row>
+    <row r="15" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="122" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+    </row>
+    <row r="16" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="122" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+    </row>
+    <row r="17" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="122" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="134"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+    </row>
+    <row r="18" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="122" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="131">
+        <f>SUM(B18:K18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="129" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="135"/>
+    </row>
+    <row r="20" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="122" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="134"/>
+      <c r="C20" s="134"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+    </row>
+    <row r="21" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="122" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="136"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="136"/>
+    </row>
+    <row r="22" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="122" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="134"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="134"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="134"/>
+      <c r="I22" s="134"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="134"/>
+    </row>
+    <row r="23" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="122" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="134"/>
+      <c r="C23" s="134"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="137">
+        <f>SUM(B23:K23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="129" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="135"/>
+    </row>
+    <row r="25" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="122" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="134"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
+    </row>
+    <row r="26" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="122" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="138"/>
+    </row>
+    <row r="27" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="122" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="126"/>
+    </row>
+    <row r="28" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="122" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="126"/>
+      <c r="C28" s="126"/>
+      <c r="D28" s="126"/>
+      <c r="E28" s="126"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="126"/>
+      <c r="H28" s="126"/>
+      <c r="I28" s="126"/>
+      <c r="J28" s="126"/>
+      <c r="K28" s="126"/>
+      <c r="L28" s="137">
+        <f>SUM(B28:K28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
+    </row>
+    <row r="30" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="122" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" s="134"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="134"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="134"/>
+      <c r="J30" s="134"/>
+      <c r="K30" s="134"/>
+      <c r="L30" s="131">
+        <f>L13+L28+L23+L18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="129" t="s">
+        <v>183</v>
+      </c>
+      <c r="B31" s="135"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="135"/>
+      <c r="L31" s="139"/>
+    </row>
+    <row r="32" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="136"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="136"/>
+      <c r="G32" s="136"/>
+      <c r="H32" s="136"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="136"/>
+      <c r="K32" s="136"/>
+    </row>
+    <row r="33" spans="1:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="140"/>
+    </row>
+    <row r="34" spans="1:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="141"/>
+      <c r="C34" s="141"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="141"/>
+      <c r="H34" s="141"/>
+      <c r="I34" s="141"/>
+      <c r="J34" s="141"/>
+      <c r="K34" s="141"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>